--- a/reports/relatorio_2026_02.xlsx
+++ b/reports/relatorio_2026_02.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -530,11 +530,7 @@
           <t>EDP</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>R$ 0,15</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>20/02/2026</t>
@@ -542,71 +538,127 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>extraido</t>
+          <t>dados incompletos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fwd: EDP - FATURAS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>downloads\pdfs\2026\BANDFATELBT01_00000000112503000471_0000000996A.pdf</t>
-        </is>
-      </c>
+          <t>EDP - FATURAS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adilson Mota</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R$ 0,15</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dados incompletos</t>
+          <t>extraido</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fwd: Extrato de aluguel de locação</t>
+          <t>Fwd: EDP - FATURAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>downloads\pdfs\2026\8591_0_9_4_5112122841_extrato_grupokaza.pdf</t>
+          <t>downloads\pdfs\2026\BANDFATELBT01_00000000112503000471_0000000996A.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CPFL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R$ 244,78</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>extraido corpo email</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Conta por e-mail CPFL - Protocolo: 0390677452</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adilson Mota</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dados incompletos</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fwd: Extrato de aluguel de locação</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>downloads\pdfs\2026\8591_0_9_4_5112122841_extrato_grupokaza.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>GRUPO KAZA JACAREÍ</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>dados incompletos</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Extrato de aluguel de locação</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>downloads\pdfs\2026\8591_0_9_4_5112122841_extrato_grupokaza.pdf</t>
         </is>
